--- a/output_data/AC_Load_OG.xlsx
+++ b/output_data/AC_Load_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>125.594012499393</v>
+        <v>126.045839365569</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>101.2840076409449</v>
+        <v>100.0612300280494</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>67.87135899524039</v>
+        <v>66.56683050686786</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.36884652689811</v>
+        <v>73.44578781496999</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>88.82424516977107</v>
+        <v>87.63135302239944</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91.46887064240595</v>
+        <v>92.84386185507925</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>163.3189675352771</v>
+        <v>164.3760886430804</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>335.6956689719093</v>
+        <v>338.4843885866073</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>465.6006252730909</v>
+        <v>463.2149309879003</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>599.2509777933467</v>
+        <v>595.852779102376</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>564.1307428433259</v>
+        <v>569.7536210193132</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>545.32619507223</v>
+        <v>560.037570133316</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>552.6392601469236</v>
+        <v>536.7576628988903</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>563.26787011564</v>
+        <v>564.2019868957021</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>553.3463384051935</v>
+        <v>560.3544912746552</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>527.7704721878699</v>
+        <v>519.6759486565786</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>488.2847403801659</v>
+        <v>492.2401932846081</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>458.8408622319121</v>
+        <v>456.5920143315897</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>417.0559477228034</v>
+        <v>414.514784254584</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>381.0154616771773</v>
+        <v>387.0956280037905</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>341.609881727023</v>
+        <v>327.8770962767575</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>290.3857182874813</v>
+        <v>280.8350192173322</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>238.5277088816471</v>
+        <v>233.9570922942397</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>198.9405217184964</v>
+        <v>197.7216644571128</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/AC_Load_OG.xlsx
+++ b/output_data/AC_Load_OG.xlsx
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>126.045839365569</v>
+        <v>127.0752200825277</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>100.0612300280494</v>
+        <v>101.0133716055155</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>66.56683050686786</v>
+        <v>67.11075882850862</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>73.44578781496999</v>
+        <v>72.01217534798239</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>87.63135302239944</v>
+        <v>88.41697129862514</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92.84386185507925</v>
+        <v>94.33921377434898</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164.3760886430804</v>
+        <v>164.8221626019601</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>338.4843885866073</v>
+        <v>334.0618546499501</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>463.2149309879003</v>
+        <v>474.4455276976772</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>595.852779102376</v>
+        <v>590.1205120069405</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>569.7536210193132</v>
+        <v>573.3730127388939</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>560.037570133316</v>
+        <v>569.7435454359877</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>536.7576628988903</v>
+        <v>548.9883048317027</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>564.2019868957021</v>
+        <v>580.0297499054043</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>560.3544912746552</v>
+        <v>561.0418907125601</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>519.6759486565786</v>
+        <v>525.9553505475685</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>492.2401932846081</v>
+        <v>483.2918246996279</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>456.5920143315897</v>
+        <v>460.4599878438494</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>414.514784254584</v>
+        <v>413.028758788601</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>387.0956280037905</v>
+        <v>395.5971591700652</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>327.8770962767575</v>
+        <v>329.5597552694377</v>
       </c>
     </row>
     <row r="23">
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>280.8350192173322</v>
+        <v>287.6749813314223</v>
       </c>
     </row>
     <row r="24">
@@ -621,7 +621,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>233.9570922942397</v>
+        <v>228.045234210927</v>
       </c>
     </row>
     <row r="25">
@@ -629,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>197.7216644571128</v>
+        <v>199.6673453787627</v>
       </c>
     </row>
     <row r="26">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>126</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/AC_Load_OG.xlsx
+++ b/output_data/AC_Load_OG.xlsx
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
